--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/panel_11/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.68604</v>
+        <v>16.69104</v>
       </c>
       <c r="D2" t="n">
-        <v>16.14938</v>
+        <v>16.44191</v>
       </c>
       <c r="E2" t="n">
-        <v>16.4646</v>
+        <v>16.48455</v>
       </c>
       <c r="F2" t="n">
-        <v>42.59828</v>
+        <v>42.56791</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0509</v>
+        <v>0.04933</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78125</v>
+        <v>1.81245</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.45229</v>
+        <v>16.51653</v>
       </c>
       <c r="D3" t="n">
-        <v>16.27154</v>
+        <v>16.36389</v>
       </c>
       <c r="E3" t="n">
-        <v>16.84186</v>
+        <v>16.42879</v>
       </c>
       <c r="F3" t="n">
-        <v>41.67829</v>
+        <v>42.69824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05045</v>
+        <v>0.04989</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81662</v>
+        <v>1.80319</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.81532</v>
+        <v>16.80672</v>
       </c>
       <c r="D4" t="n">
-        <v>16.38126</v>
+        <v>16.25547</v>
       </c>
       <c r="E4" t="n">
-        <v>16.67263</v>
+        <v>16.7074</v>
       </c>
       <c r="F4" t="n">
-        <v>42.17762</v>
+        <v>42.07801</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05118</v>
+        <v>0.04986</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78997</v>
+        <v>1.79055</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89981</v>
+        <v>16.50915</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10643</v>
+        <v>16.06352</v>
       </c>
       <c r="E6" t="n">
-        <v>16.35399</v>
+        <v>16.40475</v>
       </c>
       <c r="F6" t="n">
-        <v>21.79969</v>
+        <v>21.78812</v>
       </c>
       <c r="G6" t="n">
-        <v>34.27801</v>
+        <v>34.46582</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.42224</v>
+        <v>16.35411</v>
       </c>
       <c r="D7" t="n">
-        <v>16.07855</v>
+        <v>15.45681</v>
       </c>
       <c r="E7" t="n">
-        <v>16.39794</v>
+        <v>15.92706</v>
       </c>
       <c r="F7" t="n">
-        <v>21.38984</v>
+        <v>21.70819</v>
       </c>
       <c r="G7" t="n">
-        <v>33.93088</v>
+        <v>33.62345</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.26882</v>
+        <v>16.93944</v>
       </c>
       <c r="D8" t="n">
-        <v>15.93988</v>
+        <v>15.63338</v>
       </c>
       <c r="E8" t="n">
-        <v>16.19588</v>
+        <v>16.31076</v>
       </c>
       <c r="F8" t="n">
-        <v>21.72065</v>
+        <v>21.57774</v>
       </c>
       <c r="G8" t="n">
-        <v>34.20553</v>
+        <v>34.32917</v>
       </c>
     </row>
   </sheetData>
